--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899D5EC0-1F9A-7345-A159-82140FE5E63F}"/>
+  <xr:revisionPtr revIDLastSave="329" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E3B5ACA-33F5-264A-A616-F072ADF4DB52}"/>
   <bookViews>
-    <workbookView xWindow="12620" yWindow="4000" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="3540" windowWidth="32460" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="361">
   <si>
     <t>ID canonique</t>
   </si>
@@ -869,9 +869,6 @@
     <t>Lili Marleen;</t>
   </si>
   <si>
-    <t xml:space="preserve">rwf-1981-lili-marleen; </t>
-  </si>
-  <si>
     <t>Fengler</t>
   </si>
   <si>
@@ -1282,6 +1279,116 @@
   </si>
   <si>
     <t>Collaborations ponctuelles</t>
+  </si>
+  <si>
+    <t>Barbara Sukowa</t>
+  </si>
+  <si>
+    <t>pers-barbara-sukowa</t>
+  </si>
+  <si>
+    <t>Sukowa</t>
+  </si>
+  <si>
+    <t>Actrive</t>
+  </si>
+  <si>
+    <t>Période tardive</t>
+  </si>
+  <si>
+    <t>Berlin Alexanderplatz; Lola une femme allemande</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> film-1980-berlin-alexanderplatz</t>
+  </si>
+  <si>
+    <t>film-1981-lili-marleen</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">démarre à la télévision en 1974. Repérée par RWF au théâtre, elle tourne en 1980 dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Berlin Alexanderplatz. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Commence sa carrière cinématoghique avec </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Les années de plomb de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">von Trota. Tient le rôle principal de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Lola une femme allemande. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Prix d'interprétation à Cannes pour son rôle de Rosa Luxembourg dans le film de Margarethe Von Trotta.Carrière internationale. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Figure de la fragilité et de l'innocence instinctive dans </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Berlin Alexanderplatz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, ellest pour Claire Kaiser "le double trivial et non sophistiqué" d'Hanna Schygulla. Allie le grotesque et la grâce, la pureté et l'érotisme. Fait partie des corps vecteurs de l'Histoire. </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1456,7 +1563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1540,6 +1647,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1566,14 +1676,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N32" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N32">
-    <sortCondition ref="C1:C32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N33" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N33">
+    <sortCondition ref="C1:C33"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
@@ -1790,8 +1896,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1866,16 +1972,16 @@
         <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>93</v>
@@ -1909,7 +2015,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>171</v>
@@ -1949,13 +2055,13 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -1976,42 +2082,42 @@
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>285</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>286</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
@@ -2029,7 +2135,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>18</v>
@@ -2069,7 +2175,7 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>27</v>
@@ -2109,16 +2215,16 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>102</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>103</v>
@@ -2148,10 +2254,10 @@
         <v>188</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>18</v>
@@ -2191,7 +2297,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>151</v>
@@ -2220,25 +2326,25 @@
     </row>
     <row r="11" spans="1:14" ht="97" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="25"/>
@@ -2248,23 +2354,23 @@
     </row>
     <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2276,42 +2382,42 @@
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="27" t="s">
         <v>271</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>272</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
@@ -2319,7 +2425,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>65</v>
@@ -2329,13 +2435,13 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
@@ -2367,13 +2473,13 @@
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>109</v>
@@ -2406,16 +2512,16 @@
         <v>73</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>74</v>
@@ -2436,28 +2542,28 @@
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -2481,7 +2587,7 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>198</v>
@@ -2496,7 +2602,7 @@
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>201</v>
@@ -2510,17 +2616,17 @@
         <v>114</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>116</v>
@@ -2557,16 +2663,16 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>19</v>
@@ -2597,7 +2703,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>27</v>
@@ -2636,19 +2742,19 @@
         <v>134</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>135</v>
@@ -2678,13 +2784,13 @@
         <v>180</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>181</v>
@@ -2704,26 +2810,26 @@
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2746,16 +2852,16 @@
         <v>46</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>49</v>
@@ -2789,7 +2895,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>83</v>
@@ -2798,13 +2904,13 @@
         <v>84</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>85</v>
@@ -2857,101 +2963,99 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="72" customHeight="1">
-      <c r="A28" s="26" t="s">
-        <v>252</v>
+      <c r="A28" s="29" t="s">
+        <v>352</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>247</v>
+        <v>351</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>255</v>
+        <v>353</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>246</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>47</v>
+        <v>355</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>27</v>
+        <v>354</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>250</v>
+        <v>28</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>253</v>
+        <v>359</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>251</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N28" s="3"/>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>138</v>
+      <c r="A29" s="26" t="s">
+        <v>252</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>139</v>
+        <v>247</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>141</v>
+        <v>246</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>344</v>
+        <v>47</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>143</v>
+        <v>248</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>253</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>144</v>
+        <v>254</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="18" t="s">
-        <v>145</v>
+        <v>249</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>146</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="72" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>27</v>
@@ -2960,95 +3064,135 @@
         <v>28</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="L30" s="3"/>
+      <c r="M30" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="72" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="19" t="s">
+      <c r="L31" s="3"/>
+      <c r="M31" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="N30" s="3" t="s">
+      <c r="N31" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="72" customHeight="1">
-      <c r="A31" s="7" t="s">
+    <row r="32" spans="1:14" ht="72" customHeight="1">
+      <c r="A32" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G31" s="4" t="s">
+      <c r="E32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4" t="s">
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K32" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="18" t="s">
+      <c r="L32" s="4"/>
+      <c r="M32" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="N31" s="4" t="s">
+      <c r="N32" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="32" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
-      <c r="A32" s="21" t="s">
+    <row r="33" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
+      <c r="A33" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B33" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C33" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D33" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F33" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G33" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H33" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="M33" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="I32" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="K32" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="M32" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="N32" s="21" t="s">
+      <c r="N33" s="21" t="s">
         <v>261</v>
       </c>
     </row>
@@ -3063,7 +3207,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="329" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E3B5ACA-33F5-264A-A616-F072ADF4DB52}"/>
+  <xr:revisionPtr revIDLastSave="330" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C83EBB10-9EC9-7C4F-8712-D57E146834C9}"/>
   <bookViews>
     <workbookView xWindow="4560" yWindow="3540" windowWidth="32460" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="362">
   <si>
     <t>ID canonique</t>
   </si>
@@ -1389,6 +1389,9 @@
       </rPr>
       <t xml:space="preserve">, ellest pour Claire Kaiser "le double trivial et non sophistiqué" d'Hanna Schygulla. Allie le grotesque et la grâce, la pureté et l'érotisme. Fait partie des corps vecteurs de l'Histoire. </t>
     </r>
+  </si>
+  <si>
+    <t>Sukowa.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2998,7 +3001,9 @@
       <c r="M28" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="N28" s="3"/>
+      <c r="N28" s="3" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
       <c r="A29" s="26" t="s">

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C83EBB10-9EC9-7C4F-8712-D57E146834C9}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49E56C20-9FC3-FA44-BD0B-7D39188DB700}"/>
   <bookViews>
     <workbookView xWindow="4560" yWindow="3540" windowWidth="32460" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="363">
   <si>
     <t>ID canonique</t>
   </si>
@@ -671,9 +671,6 @@
   </si>
   <si>
     <t>film-1969-l-amour-est-plus-froid-que-la-mort; film-1970-le-voyage-a-niklashausen; film-1970-les-dieux-de-la-peste; film-1974-effi-briest</t>
-  </si>
-  <si>
-    <t>Strätz.jpg</t>
   </si>
   <si>
     <t>pers-volker-spengler</t>
@@ -1392,6 +1389,12 @@
   </si>
   <si>
     <t>Sukowa.jpeg</t>
+  </si>
+  <si>
+    <t>Stratz.jpg</t>
+  </si>
+  <si>
+    <t>Fassbinder.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1649,10 +1652,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1677,6 +1680,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1899,6 +1906,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -1975,16 +1985,16 @@
         <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>93</v>
@@ -2018,7 +2028,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>171</v>
@@ -2037,7 +2047,7 @@
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>176</v>
@@ -2058,13 +2068,13 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -2085,42 +2095,42 @@
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
@@ -2138,7 +2148,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>18</v>
@@ -2178,7 +2188,7 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>27</v>
@@ -2197,7 +2207,7 @@
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>166</v>
@@ -2218,16 +2228,16 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>102</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>103</v>
@@ -2257,16 +2267,16 @@
         <v>188</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>189</v>
@@ -2300,7 +2310,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>151</v>
@@ -2329,25 +2339,25 @@
     </row>
     <row r="11" spans="1:14" ht="97" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="25"/>
@@ -2357,23 +2367,23 @@
     </row>
     <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2381,46 +2391,48 @@
       <c r="K12" s="25"/>
       <c r="L12" s="3"/>
       <c r="M12" s="18"/>
-      <c r="N12" s="3"/>
+      <c r="N12" s="3" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="27" t="s">
         <v>270</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>271</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
@@ -2428,7 +2440,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>65</v>
@@ -2438,13 +2450,13 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
@@ -2455,7 +2467,7 @@
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>69</v>
@@ -2469,20 +2481,20 @@
         <v>108</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>109</v>
@@ -2495,7 +2507,7 @@
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>112</v>
@@ -2515,16 +2527,16 @@
         <v>73</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>74</v>
@@ -2545,28 +2557,28 @@
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -2590,7 +2602,7 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>198</v>
@@ -2605,7 +2617,7 @@
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>201</v>
@@ -2619,17 +2631,17 @@
         <v>114</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>116</v>
@@ -2645,7 +2657,7 @@
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>120</v>
@@ -2666,16 +2678,16 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>19</v>
@@ -2706,7 +2718,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>27</v>
@@ -2745,19 +2757,19 @@
         <v>134</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>135</v>
@@ -2767,7 +2779,7 @@
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>137</v>
@@ -2787,13 +2799,13 @@
         <v>180</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>313</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>181</v>
@@ -2813,26 +2825,26 @@
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2855,16 +2867,16 @@
         <v>46</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>49</v>
@@ -2898,7 +2910,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>83</v>
@@ -2907,13 +2919,13 @@
         <v>84</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>85</v>
@@ -2959,64 +2971,64 @@
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>211</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="72" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>353</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>28</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>356</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>357</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="N28" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
@@ -3026,23 +3038,23 @@
         <v>27</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J29" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="K29" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>254</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="72" customHeight="1">
@@ -3060,7 +3072,7 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>27</v>
@@ -3100,7 +3112,7 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>27</v>
@@ -3119,7 +3131,7 @@
       </c>
       <c r="L31" s="3"/>
       <c r="M31" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>32</v>
@@ -3127,20 +3139,20 @@
     </row>
     <row r="32" spans="1:14" ht="72" customHeight="1">
       <c r="A32" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>18</v>
@@ -3150,59 +3162,60 @@
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K32" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>217</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
       <c r="A33" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="B33" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="C33" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="D33" s="21" t="s">
         <v>258</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>259</v>
       </c>
       <c r="F33" s="21" t="s">
         <v>47</v>
       </c>
       <c r="G33" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="M33" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="N33" s="21" t="s">
         <v>260</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="I33" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="J33" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="K33" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="M33" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="N33" s="21" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="19" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3220,79 +3233,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
-      <c r="A1" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="A1" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>220</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>221</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>222</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>223</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>224</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>225</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>226</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>227</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>228</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>229</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>230</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>231</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>232</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>233</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -3302,5 +3315,6 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="338" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49E56C20-9FC3-FA44-BD0B-7D39188DB700}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC3EEF60-669E-8641-91EC-E941A7DC3B50}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="3540" windowWidth="32460" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8920" yWindow="3460" windowWidth="32460" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entourage" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="371">
   <si>
     <t>ID canonique</t>
   </si>
@@ -1058,9 +1058,6 @@
     <t>perso-Helmut-Fassbinder</t>
   </si>
   <si>
-    <t xml:space="preserve">Père de RWF. Médecin, amateur de poésie. Il se spérare de Liselotte (Lilo), la mère de RWD, et quitte Munich pour Francfort. Il vut de la rente que lui procure la location d'appartements de rendements, essentiellement auprès de travailleurs immigrés. Adulte, RWF refuse tout contact avec lui d'après Katz. </t>
-  </si>
-  <si>
     <t>Udo Kier</t>
   </si>
   <si>
@@ -1395,6 +1392,33 @@
   </si>
   <si>
     <t>Fassbinder.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Père de RWF. Médecin, amateur de poésie. Il se spérare de Liselotte (Lilo), la mère de RWD, et quitte Munich pour Cologne. Il vit de la rente que lui procure la location d'appartements de rendements, essentiellement auprès de travailleurs immigrés. Adulte, RWF refuse tout contact avec lui d'après Katz. </t>
+  </si>
+  <si>
+    <t>Karl Schyedt</t>
+  </si>
+  <si>
+    <t>Scheydt</t>
+  </si>
+  <si>
+    <t>Karl</t>
+  </si>
+  <si>
+    <t>pers-karl-schyedt</t>
+  </si>
+  <si>
+    <t>jeu - assistance technique</t>
+  </si>
+  <si>
+    <t>acteur</t>
+  </si>
+  <si>
+    <t>film-1970-le-voyage-a-niklashausen; film-1970-le-soldat-americain; film-1971-prenez-garde-a-la-sainte-putain; film-1972-le-marchand-des-quatre-saisons;  film-1972-huit-heures-ne-font-pas-un-jour; film-1973-gibier-de-passage; film-1974-martha; film-1974-tous-les-autres-s-appellent-ali; film-1975-le-droit-du-plus-fort; film-1977-la-femme-du-chef-de-gare; film-1978-l-annee-des-treize-lunes</t>
+  </si>
+  <si>
+    <t>Scheydt.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1687,9 +1711,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N33" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N33">
-    <sortCondition ref="C1:C33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N34" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N34">
+    <sortCondition ref="C1:C34"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
@@ -1909,7 +1933,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -1985,16 +2009,16 @@
         <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>93</v>
@@ -2028,7 +2052,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>171</v>
@@ -2068,13 +2092,13 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -2098,17 +2122,17 @@
         <v>281</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>280</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>18</v>
@@ -2148,7 +2172,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>18</v>
@@ -2188,7 +2212,7 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>27</v>
@@ -2228,16 +2252,16 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>102</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>103</v>
@@ -2267,10 +2291,10 @@
         <v>188</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>18</v>
@@ -2310,7 +2334,7 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>151</v>
@@ -2357,7 +2381,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>291</v>
+        <v>362</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="25"/>
@@ -2367,23 +2391,23 @@
     </row>
     <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>287</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2392,7 +2416,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="18"/>
       <c r="N12" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
@@ -2410,7 +2434,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>265</v>
@@ -2440,7 +2464,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>65</v>
@@ -2450,13 +2474,13 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
@@ -2488,13 +2512,13 @@
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>109</v>
@@ -2527,16 +2551,16 @@
         <v>73</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>74</v>
@@ -2557,28 +2581,28 @@
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -2602,7 +2626,7 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>198</v>
@@ -2617,7 +2641,7 @@
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>201</v>
@@ -2638,10 +2662,10 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>116</v>
@@ -2678,16 +2702,16 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>19</v>
@@ -2718,7 +2742,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>27</v>
@@ -2757,19 +2781,19 @@
         <v>134</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>135</v>
@@ -2799,13 +2823,13 @@
         <v>180</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>181</v>
@@ -2825,26 +2849,26 @@
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2855,264 +2879,256 @@
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>43</v>
+        <v>366</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>44</v>
+        <v>363</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>364</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>349</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>48</v>
+        <v>368</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
       <c r="K25" s="9" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
       <c r="L25" s="3"/>
-      <c r="M25" s="18" t="s">
-        <v>52</v>
-      </c>
+      <c r="M25" s="18"/>
       <c r="N25" s="3" t="s">
-        <v>53</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="72" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="F26" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>306</v>
+        <v>49</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>276</v>
+        <v>50</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>85</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="L26" s="3"/>
       <c r="M26" s="18" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="72" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>207</v>
+        <v>84</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="L27" s="3"/>
+        <v>275</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M27" s="18" t="s">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>361</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="72" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>351</v>
+      <c r="A28" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>350</v>
+        <v>203</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>352</v>
+        <v>204</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>205</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>354</v>
+        <v>206</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>353</v>
+        <v>27</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>358</v>
+        <v>208</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>355</v>
+        <v>209</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>356</v>
+        <v>210</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="18" t="s">
-        <v>359</v>
+        <v>237</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>251</v>
+      <c r="A29" s="28" t="s">
+        <v>350</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>246</v>
+        <v>349</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>254</v>
+        <v>351</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>245</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>47</v>
+        <v>353</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J29" s="20" t="s">
-        <v>252</v>
+        <v>357</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>253</v>
+        <v>355</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="18" t="s">
-        <v>248</v>
+        <v>358</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>250</v>
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="72" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>138</v>
+      <c r="A30" s="26" t="s">
+        <v>251</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>139</v>
+        <v>246</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>342</v>
+        <v>47</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>28</v>
+        <v>249</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>143</v>
+        <v>247</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>252</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="18" t="s">
-        <v>145</v>
+        <v>248</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>146</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="72" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>27</v>
@@ -3121,95 +3137,135 @@
         <v>28</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="L31" s="3"/>
+      <c r="M31" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="72" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K31" s="9" t="s">
+      <c r="K32" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L31" s="3"/>
-      <c r="M31" s="19" t="s">
+      <c r="L32" s="3"/>
+      <c r="M32" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="N31" s="3" t="s">
+      <c r="N32" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="72" customHeight="1">
-      <c r="A32" s="7" t="s">
+    <row r="33" spans="1:14" ht="72" customHeight="1">
+      <c r="A33" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B33" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C33" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4" t="s">
+      <c r="I33" s="4"/>
+      <c r="J33" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K33" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="L32" s="4"/>
-      <c r="M32" s="18" t="s">
+      <c r="L33" s="4"/>
+      <c r="M33" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="N32" s="4" t="s">
+      <c r="N33" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="33" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
+      <c r="A34" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B34" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C34" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D34" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F34" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G34" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H34" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I34" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="J33" s="21" t="s">
+      <c r="J34" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="K33" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="M33" s="22" t="s">
+      <c r="K34" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="M34" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="N33" s="21" t="s">
+      <c r="N34" s="21" t="s">
         <v>260</v>
       </c>
     </row>

--- a/RWF_Entourage.xlsx
+++ b/RWF_Entourage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="356" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC3EEF60-669E-8641-91EC-E941A7DC3B50}"/>
+  <xr:revisionPtr revIDLastSave="371" documentId="13_ncr:1_{F6122F05-6BF8-2143-A03F-6CEF85960A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{307E2B49-7F2C-6045-B246-0992E153AE1F}"/>
   <bookViews>
     <workbookView xWindow="8920" yWindow="3460" windowWidth="32460" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="377">
   <si>
     <t>ID canonique</t>
   </si>
@@ -235,9 +235,6 @@
   </si>
   <si>
     <t>John</t>
-  </si>
-  <si>
-    <t>Huit heures ne font pas un jour; Maman Küsters s’en va au ciel; Despair; L’Année des treize lunes; Le Mariage de Maria Braun; Berlin Alexanderplatz; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande</t>
   </si>
   <si>
     <t>film-1972-huit-heures-ne-font-pas-un-jour; film-1975-maman-kusters-s-en-va-au-ciel; film-1978-despair; film-1978-l-annee-des-treize-lunes; film-1979-le-mariage-de-maria-braun; film-1980-berlin-alexanderplatz; film-1981-le-secret-de-veronika-voss; film-1981-lili-marleen; film-1981-lola-une-femme-allemande</t>
@@ -1419,6 +1416,27 @@
   </si>
   <si>
     <t>Scheydt.jpeg</t>
+  </si>
+  <si>
+    <t>pers-herb-andress</t>
+  </si>
+  <si>
+    <t>Herb Andress</t>
+  </si>
+  <si>
+    <t>Andress</t>
+  </si>
+  <si>
+    <t>Herb</t>
+  </si>
+  <si>
+    <t>Prenez garde à la sainte putain; huit heures ne font pas un jour; Lili Marleen</t>
+  </si>
+  <si>
+    <t>film-1971-prenez-garde-a-la-sainte-putain; film-1972-huit-heures-ne-font-pas-un-jour; film-1981-lili-marleen</t>
+  </si>
+  <si>
+    <t>Andress.png</t>
   </si>
 </sst>
 </file>
@@ -1711,9 +1729,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N34" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N34">
-    <sortCondition ref="C1:C34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EntourageV30" displayName="EntourageV30" ref="A1:N35" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N35">
+    <sortCondition ref="C1:C35"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID canonique"/>
@@ -1933,7 +1951,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -1997,84 +2015,84 @@
     </row>
     <row r="2" spans="1:14" ht="72" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>95</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="72" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="72" customHeight="1">
@@ -2092,13 +2110,13 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -2119,269 +2137,269 @@
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="72" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="23" t="s">
         <v>123</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>124</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="72" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="72" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="N10" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="97" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="25"/>
@@ -2391,23 +2409,23 @@
     </row>
     <row r="12" spans="1:14" ht="97" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2416,47 +2434,47 @@
       <c r="L12" s="3"/>
       <c r="M12" s="18"/>
       <c r="N12" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="72" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="27" t="s">
         <v>269</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>270</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="72" customHeight="1">
@@ -2464,7 +2482,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>65</v>
@@ -2474,701 +2492,693 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3"/>
+      <c r="K14" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="72" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>107</v>
+        <v>370</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>238</v>
+        <v>372</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>239</v>
+        <v>373</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>109</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>110</v>
+        <v>374</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>111</v>
+        <v>375</v>
       </c>
       <c r="L15" s="3"/>
-      <c r="M15" s="18" t="s">
-        <v>236</v>
-      </c>
+      <c r="M15" s="18"/>
       <c r="N15" s="3" t="s">
-        <v>112</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>72</v>
+        <v>237</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>316</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="18" t="s">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>297</v>
+        <v>69</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>296</v>
+        <v>72</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="9"/>
+        <v>320</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="L17" s="3"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="3"/>
+      <c r="M17" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="18" spans="1:14" ht="72" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>194</v>
+        <v>296</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E18" s="3"/>
+        <v>295</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="F18" s="3" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="H18" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="I18" s="3"/>
-      <c r="J18" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>200</v>
-      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="9"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>201</v>
-      </c>
+      <c r="M18" s="18"/>
+      <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="72" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="L19" s="3"/>
-      <c r="M19" s="18" t="s">
-        <v>243</v>
+      <c r="M19" s="19" t="s">
+        <v>311</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="72" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>18</v>
+        <v>334</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>320</v>
+        <v>115</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>337</v>
+        <v>116</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="18" t="s">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>38</v>
+        <v>336</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="18" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="132" customHeight="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="72" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>315</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>206</v>
+        <v>345</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>309</v>
+        <v>27</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>314</v>
+        <v>37</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>347</v>
+        <v>38</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="18" t="s">
-        <v>242</v>
+        <v>41</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="72" customHeight="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="132" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>344</v>
+        <v>205</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>181</v>
+        <v>313</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="9"/>
+        <v>346</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="18" t="s">
-        <v>183</v>
+        <v>241</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="72" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>302</v>
+        <v>176</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>299</v>
+        <v>177</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>300</v>
+        <v>178</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E24" s="3"/>
+        <v>179</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="F24" s="3" t="s">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="I24" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="J24" s="3"/>
       <c r="K24" s="9"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="3"/>
+      <c r="M24" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="72" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>366</v>
+        <v>301</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>363</v>
+        <v>298</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>364</v>
+        <v>299</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>365</v>
+        <v>300</v>
       </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="G25" s="3" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="9" t="s">
-        <v>369</v>
-      </c>
+      <c r="K25" s="9"/>
       <c r="L25" s="3"/>
       <c r="M25" s="18"/>
-      <c r="N25" s="3" t="s">
-        <v>370</v>
-      </c>
+      <c r="N25" s="3"/>
     </row>
     <row r="26" spans="1:14" ht="72" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>43</v>
+        <v>365</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>44</v>
+        <v>362</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>45</v>
+        <v>363</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>348</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>48</v>
+        <v>367</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="9" t="s">
-        <v>51</v>
+        <v>368</v>
       </c>
       <c r="L26" s="3"/>
-      <c r="M26" s="18" t="s">
-        <v>52</v>
-      </c>
+      <c r="M26" s="18"/>
       <c r="N26" s="3" t="s">
-        <v>53</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="72" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E27" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="F27" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>305</v>
+        <v>49</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>276</v>
+        <v>50</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>85</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="L27" s="3"/>
       <c r="M27" s="18" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="72" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>206</v>
+        <v>343</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="L28" s="3"/>
+        <v>274</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="M28" s="18" t="s">
-        <v>237</v>
+        <v>85</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>360</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="72" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>350</v>
+      <c r="A29" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>351</v>
+        <v>203</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>353</v>
+        <v>205</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>352</v>
+        <v>27</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>357</v>
+        <v>207</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>354</v>
+        <v>208</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>355</v>
+        <v>209</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="18" t="s">
-        <v>358</v>
+        <v>236</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="72" customHeight="1">
-      <c r="A30" s="26" t="s">
-        <v>251</v>
+      <c r="A30" s="28" t="s">
+        <v>349</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>246</v>
+        <v>348</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>254</v>
+        <v>350</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>245</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>47</v>
+        <v>352</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>27</v>
+        <v>351</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J30" s="20" t="s">
-        <v>252</v>
+        <v>356</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>253</v>
+        <v>354</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="18" t="s">
-        <v>248</v>
+        <v>357</v>
       </c>
       <c r="N30" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="72" customHeight="1">
+      <c r="A31" s="26" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="72" customHeight="1">
-      <c r="A31" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="B31" s="3" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>341</v>
+        <v>47</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>28</v>
+        <v>248</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>143</v>
+        <v>246</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>144</v>
+        <v>252</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" s="18" t="s">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>146</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="72" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>27</v>
@@ -3177,96 +3187,136 @@
         <v>28</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="L32" s="3"/>
+      <c r="M32" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="72" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="K33" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="N32" s="3" t="s">
+      <c r="L33" s="3"/>
+      <c r="M33" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="N33" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="72" customHeight="1">
-      <c r="A33" s="7" t="s">
+    <row r="34" spans="1:14" ht="72" customHeight="1">
+      <c r="A34" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="C34" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E34" s="4"/>
+      <c r="F34" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4" t="s">
+      <c r="K34" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="L34" s="4"/>
+      <c r="M34" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="N34" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
-      <c r="A34" s="21" t="s">
+    </row>
+    <row r="35" spans="1:14" s="21" customFormat="1" ht="108" customHeight="1">
+      <c r="A35" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="C35" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="D35" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="F35" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G34" s="21" t="s">
+      <c r="H35" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="J35" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="M35" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="N35" s="21" t="s">
         <v>259</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="J34" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="K34" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="M34" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="N34" s="21" t="s">
-        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -3290,7 +3340,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -3298,70 +3348,70 @@
     </row>
     <row r="3" spans="1:4" ht="34" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>220</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>221</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>222</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>223</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>224</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
       <c r="A6" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>225</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>226</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>227</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>228</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>229</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>230</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>231</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
